--- a/data/trans_bre/IP04F-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP04F-Clase-trans_bre.xlsx
@@ -601,22 +601,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-6,66; 14,24</t>
+          <t>-5,02; 15,2</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-6,85; 11,61</t>
+          <t>-5,6; 12,53</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-27,05; 91,26</t>
+          <t>-20,9; 99,08</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-34,42; 89,71</t>
+          <t>-30,86; 102,92</t>
         </is>
       </c>
     </row>
@@ -661,22 +661,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-13,18; 4,31</t>
+          <t>-13,54; 4,93</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-7,22; 8,66</t>
+          <t>-6,42; 9,6</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-59,17; 29,99</t>
+          <t>-57,33; 36,31</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-40,04; 84,81</t>
+          <t>-35,6; 90,88</t>
         </is>
       </c>
     </row>
@@ -721,22 +721,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,51; 13,56</t>
+          <t>1,33; 12,44</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,31; 12,34</t>
+          <t>-3,17; 12,44</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,05; 1732,24</t>
+          <t>-12,07; 1374,81</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-47,0; 337,34</t>
+          <t>-45,13; 490,87</t>
         </is>
       </c>
     </row>
@@ -781,22 +781,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,6; 4,63</t>
+          <t>-2,44; 4,68</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-5,67; 1,34</t>
+          <t>-5,89; 1,35</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-42,03; 135,62</t>
+          <t>-40,52; 142,76</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-63,88; 30,11</t>
+          <t>-65,08; 30,17</t>
         </is>
       </c>
     </row>
@@ -841,22 +841,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-5,04; 4,19</t>
+          <t>-5,18; 4,22</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,86; 6,31</t>
+          <t>-2,09; 5,91</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-60,9; 130,52</t>
+          <t>-62,33; 137,14</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-47,63; 390,21</t>
+          <t>-50,01; 308,44</t>
         </is>
       </c>
     </row>
@@ -901,22 +901,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-6,8; 10,25</t>
+          <t>-6,66; 10,47</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-1,37; 12,13</t>
+          <t>-1,43; 12,62</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-61,07; 169,37</t>
+          <t>-53,92; 187,45</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-45,35; 1506,6</t>
+          <t>-61,5; 1129,78</t>
         </is>
       </c>
     </row>
@@ -961,22 +961,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,32; 4,15</t>
+          <t>-1,53; 4,03</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,49; 3,47</t>
+          <t>-1,64; 3,56</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-13,38; 50,2</t>
+          <t>-14,58; 53,81</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-16,5; 50,46</t>
+          <t>-17,65; 51,47</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP04F-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP04F-Clase-trans_bre.xlsx
@@ -601,22 +601,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,02; 15,2</t>
+          <t>-6,53; 14,51</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,6; 12,53</t>
+          <t>-5,72; 12,77</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-20,9; 99,08</t>
+          <t>-26,48; 95,77</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-30,86; 102,92</t>
+          <t>-31,37; 101,55</t>
         </is>
       </c>
     </row>
@@ -661,22 +661,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-13,54; 4,93</t>
+          <t>-13,92; 3,88</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-6,42; 9,6</t>
+          <t>-7,37; 8,7</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-57,33; 36,31</t>
+          <t>-58,68; 27,04</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-35,6; 90,88</t>
+          <t>-39,89; 85,4</t>
         </is>
       </c>
     </row>
@@ -721,22 +721,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,33; 12,44</t>
+          <t>1,12; 12,42</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,17; 12,44</t>
+          <t>-3,41; 12,13</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-12,07; 1374,81</t>
+          <t>-19,74; 1356,3</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-45,13; 490,87</t>
+          <t>-44,83; 365,99</t>
         </is>
       </c>
     </row>
@@ -781,22 +781,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,44; 4,68</t>
+          <t>-2,79; 4,57</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-5,89; 1,35</t>
+          <t>-5,82; 1,69</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-40,52; 142,76</t>
+          <t>-43,23; 132,6</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-65,08; 30,17</t>
+          <t>-62,29; 43,4</t>
         </is>
       </c>
     </row>
@@ -841,22 +841,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-5,18; 4,22</t>
+          <t>-5,03; 4,73</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,09; 5,91</t>
+          <t>-1,82; 6,31</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-62,33; 137,14</t>
+          <t>-59,97; 144,17</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-50,01; 308,44</t>
+          <t>-46,79; 387,48</t>
         </is>
       </c>
     </row>
@@ -901,22 +901,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-6,66; 10,47</t>
+          <t>-6,54; 10,39</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-1,43; 12,62</t>
+          <t>-1,55; 12,12</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-53,92; 187,45</t>
+          <t>-54,69; 202,92</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-61,5; 1129,78</t>
+          <t>-56,99; 1095,37</t>
         </is>
       </c>
     </row>
@@ -961,22 +961,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,53; 4,03</t>
+          <t>-1,5; 3,98</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,64; 3,56</t>
+          <t>-1,58; 3,46</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-14,58; 53,81</t>
+          <t>-14,87; 50,97</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-17,65; 51,47</t>
+          <t>-16,78; 50,69</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP04F-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP04F-Clase-trans_bre.xlsx
@@ -601,22 +601,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-6,53; 14,51</t>
+          <t>-6,66; 14,24</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,72; 12,77</t>
+          <t>-6,85; 11,61</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-26,48; 95,77</t>
+          <t>-27,05; 91,26</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-31,37; 101,55</t>
+          <t>-34,42; 89,71</t>
         </is>
       </c>
     </row>
@@ -661,22 +661,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-13,92; 3,88</t>
+          <t>-13,18; 4,31</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-7,37; 8,7</t>
+          <t>-7,22; 8,66</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-58,68; 27,04</t>
+          <t>-59,17; 29,99</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-39,89; 85,4</t>
+          <t>-40,04; 84,81</t>
         </is>
       </c>
     </row>
@@ -721,22 +721,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,12; 12,42</t>
+          <t>1,51; 13,56</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,41; 12,13</t>
+          <t>-3,31; 12,34</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-19,74; 1356,3</t>
+          <t>-3,05; 1732,24</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-44,83; 365,99</t>
+          <t>-47,0; 337,34</t>
         </is>
       </c>
     </row>
@@ -781,22 +781,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,79; 4,57</t>
+          <t>-2,6; 4,63</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-5,82; 1,69</t>
+          <t>-5,67; 1,34</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-43,23; 132,6</t>
+          <t>-42,03; 135,62</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-62,29; 43,4</t>
+          <t>-63,88; 30,11</t>
         </is>
       </c>
     </row>
@@ -841,22 +841,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-5,03; 4,73</t>
+          <t>-5,04; 4,19</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,82; 6,31</t>
+          <t>-1,86; 6,31</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-59,97; 144,17</t>
+          <t>-60,9; 130,52</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-46,79; 387,48</t>
+          <t>-47,63; 390,21</t>
         </is>
       </c>
     </row>
@@ -901,22 +901,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-6,54; 10,39</t>
+          <t>-6,8; 10,25</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-1,55; 12,12</t>
+          <t>-1,37; 12,13</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-54,69; 202,92</t>
+          <t>-61,07; 169,37</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-56,99; 1095,37</t>
+          <t>-45,35; 1506,6</t>
         </is>
       </c>
     </row>
@@ -961,22 +961,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,5; 3,98</t>
+          <t>-1,32; 4,15</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,58; 3,46</t>
+          <t>-1,49; 3,47</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-14,87; 50,97</t>
+          <t>-13,38; 50,2</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-16,78; 50,69</t>
+          <t>-16,5; 50,46</t>
         </is>
       </c>
     </row>
